--- a/results/random_forest/worst_predictions.xlsx
+++ b/results/random_forest/worst_predictions.xlsx
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n">
-        <v>13891</v>
+        <v>12704</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
         <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="T2" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Gable</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -941,8 +941,14 @@
           <t>VinylSd</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>BrkFace</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>306</v>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>Ex</t>
@@ -965,21 +971,21 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>GLQ</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1386</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -990,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>690</v>
+        <v>2042</v>
       </c>
       <c r="AL2" t="n">
-        <v>2076</v>
+        <v>2042</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -1016,7 +1022,7 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>2076</v>
+        <v>2042</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1025,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>2076</v>
+        <v>2042</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1040,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -1051,7 +1057,7 @@
         </is>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -1072,18 +1078,18 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>RFn</t>
         </is>
       </c>
       <c r="BI2" t="n">
         <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>850</v>
+        <v>1390</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -1101,10 +1107,10 @@
         </is>
       </c>
       <c r="BN2" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c r="BP2" t="n">
         <v>0</v>
@@ -1125,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BY2" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -1141,19 +1147,19 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>465000</v>
+        <v>253293</v>
       </c>
       <c r="CC2" t="n">
-        <v>346128.53</v>
+        <v>369108.246689484</v>
       </c>
       <c r="CD2" t="n">
-        <v>118871.47</v>
+        <v>-115815.246689484</v>
       </c>
       <c r="CE2" t="n">
-        <v>118871.47</v>
+        <v>115815.246689484</v>
       </c>
       <c r="CF2" t="n">
-        <v>25.56375698924731</v>
+        <v>45.72382446000641</v>
       </c>
     </row>
     <row r="3">
@@ -1166,10 +1172,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D3" t="n">
-        <v>12704</v>
+        <v>13891</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1228,20 +1234,20 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
         <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="T3" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Gable</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1259,14 +1265,8 @@
           <t>VinylSd</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>BrkFace</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>306</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>Ex</t>
@@ -1289,35 +1289,35 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>GLQ</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1386</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>Unf</t>
         </is>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Unf</t>
-        </is>
-      </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2042</v>
+        <v>690</v>
       </c>
       <c r="AL3" t="n">
-        <v>2042</v>
+        <v>2076</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>2042</v>
+        <v>2076</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2042</v>
+        <v>2076</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ3" t="n">
         <v>1</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
@@ -1396,18 +1396,18 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>RFn</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="BI3" t="n">
         <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1390</v>
+        <v>850</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="BO3" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="BP3" t="n">
         <v>0</v>
@@ -1449,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BY3" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
@@ -1465,19 +1465,19 @@
         </is>
       </c>
       <c r="CB3" t="n">
-        <v>253293</v>
+        <v>465000</v>
       </c>
       <c r="CC3" t="n">
-        <v>359284.69</v>
+        <v>362833.6896804388</v>
       </c>
       <c r="CD3" t="n">
-        <v>-105991.69</v>
+        <v>102166.3103195612</v>
       </c>
       <c r="CE3" t="n">
-        <v>105991.69</v>
+        <v>102166.3103195612</v>
       </c>
       <c r="CF3" t="n">
-        <v>41.84548724204775</v>
+        <v>21.97124953108842</v>
       </c>
     </row>
     <row r="4">
@@ -1792,16 +1792,16 @@
         <v>395000</v>
       </c>
       <c r="CC4" t="n">
-        <v>303820.13</v>
+        <v>302986.8140185743</v>
       </c>
       <c r="CD4" t="n">
-        <v>91179.87</v>
+        <v>92013.18598142575</v>
       </c>
       <c r="CE4" t="n">
-        <v>91179.87</v>
+        <v>92013.18598142575</v>
       </c>
       <c r="CF4" t="n">
-        <v>23.08351139240506</v>
+        <v>23.29447746365209</v>
       </c>
     </row>
     <row r="5">
@@ -2116,21 +2116,21 @@
         <v>451950</v>
       </c>
       <c r="CC5" t="n">
-        <v>365854.51</v>
+        <v>381280.0931723448</v>
       </c>
       <c r="CD5" t="n">
-        <v>86095.48999999999</v>
+        <v>70669.90682765516</v>
       </c>
       <c r="CE5" t="n">
-        <v>86095.48999999999</v>
+        <v>70669.90682765516</v>
       </c>
       <c r="CF5" t="n">
-        <v>19.04978205553711</v>
+        <v>15.63666485842574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="D6" t="n">
-        <v>46589</v>
+        <v>39104</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2151,12 +2151,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IR2</t>
+          <t>IR1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lvl</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Gtl</t>
+          <t>Sev</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NoRidge</t>
+          <t>ClearCr</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2196,100 +2196,100 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2Story</t>
+          <t>1Story</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
         <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>1994</v>
+        <v>1954</v>
       </c>
       <c r="T6" t="n">
         <v>2005</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Flat</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>CompShg</t>
+          <t>Membran</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>VinylSd</t>
+          <t>Plywood</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>VinylSd</t>
+          <t>Plywood</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>BrkFace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>CBlock</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>Gd</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>PConc</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Gd</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Gd</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>LwQ</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>226</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>GLQ</t>
         </is>
       </c>
-      <c r="AH6" t="n">
-        <v>1361</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Rec</t>
-        </is>
-      </c>
       <c r="AJ6" t="n">
-        <v>180</v>
+        <v>1063</v>
       </c>
       <c r="AK6" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AL6" t="n">
-        <v>1629</v>
+        <v>1385</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>1686</v>
+        <v>1363</v>
       </c>
       <c r="AR6" t="n">
-        <v>762</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>2448</v>
+        <v>1363</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
@@ -2330,32 +2330,32 @@
         <v>0</v>
       </c>
       <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
         <v>2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4</v>
       </c>
       <c r="AZ6" t="n">
         <v>1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Typ</t>
+          <t>Mod</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2368,18 +2368,18 @@
         </is>
       </c>
       <c r="BG6" t="n">
-        <v>1994</v>
+        <v>1954</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>RFn</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>711</v>
+        <v>439</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="BN6" t="n">
-        <v>517</v>
+        <v>81</v>
       </c>
       <c r="BO6" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
         <v>0</v>
@@ -2421,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BY6" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
@@ -2437,24 +2437,24 @@
         </is>
       </c>
       <c r="CB6" t="n">
-        <v>402000</v>
+        <v>241500</v>
       </c>
       <c r="CC6" t="n">
-        <v>328544.71</v>
+        <v>176295.7344069985</v>
       </c>
       <c r="CD6" t="n">
-        <v>73455.28999999998</v>
+        <v>65204.26559300153</v>
       </c>
       <c r="CE6" t="n">
-        <v>73455.28999999998</v>
+        <v>65204.26559300153</v>
       </c>
       <c r="CF6" t="n">
-        <v>18.27246019900497</v>
+        <v>26.9996958977232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="D7" t="n">
-        <v>13518</v>
+        <v>70761</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2475,12 +2475,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Reg</t>
+          <t>IR1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lvl</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Gtl</t>
+          <t>Mod</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NridgHt</t>
+          <t>ClearCr</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2520,52 +2520,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2Story</t>
+          <t>1Story</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>2008</v>
+        <v>1975</v>
       </c>
       <c r="T7" t="n">
-        <v>2009</v>
+        <v>1975</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Gable</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>CompShg</t>
+          <t>WdShngl</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>VinylSd</t>
+          <t>Plywood</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>VinylSd</t>
+          <t>Plywood</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>PConc</t>
+          <t>CBlock</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2590,30 +2590,30 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>ALQ</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>655</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>Unf</t>
         </is>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Unf</t>
-        </is>
-      </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1926</v>
+        <v>878</v>
       </c>
       <c r="AL7" t="n">
-        <v>1926</v>
+        <v>1533</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2636,42 +2636,42 @@
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>1966</v>
+        <v>1533</v>
       </c>
       <c r="AR7" t="n">
-        <v>1174</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3140</v>
+        <v>1533</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>BuiltIn</t>
+          <t>Attchd</t>
         </is>
       </c>
       <c r="BG7" t="n">
-        <v>2009</v>
+        <v>1975</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>820</v>
+        <v>576</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="BN7" t="n">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="BO7" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="BP7" t="n">
         <v>0</v>
@@ -2745,40 +2745,40 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BY7" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="CB7" t="n">
-        <v>485000</v>
+        <v>280000</v>
       </c>
       <c r="CC7" t="n">
-        <v>414156.53</v>
+        <v>217206.554642013</v>
       </c>
       <c r="CD7" t="n">
-        <v>70843.46999999997</v>
+        <v>62793.44535798696</v>
       </c>
       <c r="CE7" t="n">
-        <v>70843.46999999997</v>
+        <v>62793.44535798696</v>
       </c>
       <c r="CF7" t="n">
-        <v>14.60690103092783</v>
+        <v>22.42623048499534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n">
-        <v>8281</v>
+        <v>13518</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IR1</t>
+          <t>Reg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sawyer</t>
+          <t>NridgHt</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2844,24 +2844,24 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1Story</t>
+          <t>2Story</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
         <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>1965</v>
+        <v>2008</v>
       </c>
       <c r="T8" t="n">
-        <v>1965</v>
+        <v>2009</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Gable</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -2871,25 +2871,25 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>MetalSd</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MetalSd</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>CBlock</t>
+          <t>PConc</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2919,25 +2919,25 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Rec</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>553</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>BLQ</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="AL8" t="n">
-        <v>864</v>
+        <v>1926</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>864</v>
+        <v>1966</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>864</v>
+        <v>3140</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -2978,24 +2978,24 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1</v>
       </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
@@ -3003,31 +3003,31 @@
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>Po</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>Detchd</t>
+          <t>BuiltIn</t>
         </is>
       </c>
       <c r="BG8" t="n">
-        <v>1965</v>
+        <v>2009</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Unf</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>360</v>
+        <v>820</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="BP8" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
@@ -3063,50 +3063,46 @@
         <v>0</v>
       </c>
       <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>GdWo</t>
-        </is>
-      </c>
+      <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="inlineStr"/>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BY8" t="n">
         <v>2009</v>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>New</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="CB8" t="n">
-        <v>62383</v>
+        <v>485000</v>
       </c>
       <c r="CC8" t="n">
-        <v>124437.5</v>
+        <v>422434.3025730625</v>
       </c>
       <c r="CD8" t="n">
-        <v>-62054.5</v>
+        <v>62565.69742693746</v>
       </c>
       <c r="CE8" t="n">
-        <v>62054.5</v>
+        <v>62565.69742693746</v>
       </c>
       <c r="CF8" t="n">
-        <v>99.47341423144125</v>
+        <v>12.90014379936855</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -3114,10 +3110,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>39104</v>
+        <v>46589</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3127,12 +3123,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IR1</t>
+          <t>IR2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Lvl</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3147,12 +3143,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sev</t>
+          <t>Gtl</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ClearCr</t>
+          <t>NoRidge</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3172,52 +3168,52 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1Story</t>
+          <t>2Story</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
         <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>1954</v>
+        <v>1994</v>
       </c>
       <c r="T9" t="n">
         <v>2005</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Membran</t>
+          <t>CompShg</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Plywood</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Plywood</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>BrkFace</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3227,7 +3223,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>CBlock</t>
+          <t>PConc</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -3237,35 +3233,35 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>LwQ</t>
+          <t>GLQ</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>226</v>
+        <v>1361</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>GLQ</t>
+          <t>Rec</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1063</v>
+        <v>180</v>
       </c>
       <c r="AK9" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="AL9" t="n">
-        <v>1385</v>
+        <v>1629</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
@@ -3288,16 +3284,16 @@
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>1363</v>
+        <v>1686</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>1363</v>
+        <v>2448</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
@@ -3306,32 +3302,32 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1</v>
       </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Mod</t>
+          <t>Typ</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -3344,18 +3340,18 @@
         </is>
       </c>
       <c r="BG9" t="n">
-        <v>1954</v>
+        <v>1994</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Unf</t>
+          <t>RFn</t>
         </is>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>439</v>
+        <v>711</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -3373,10 +3369,10 @@
         </is>
       </c>
       <c r="BN9" t="n">
-        <v>81</v>
+        <v>517</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BP9" t="n">
         <v>0</v>
@@ -3397,10 +3393,10 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BY9" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
@@ -3413,19 +3409,19 @@
         </is>
       </c>
       <c r="CB9" t="n">
-        <v>241500</v>
+        <v>402000</v>
       </c>
       <c r="CC9" t="n">
-        <v>182697.16</v>
+        <v>342144.512746278</v>
       </c>
       <c r="CD9" t="n">
-        <v>58802.84</v>
+        <v>59855.48725372204</v>
       </c>
       <c r="CE9" t="n">
-        <v>58802.84</v>
+        <v>59855.48725372204</v>
       </c>
       <c r="CF9" t="n">
-        <v>24.34900207039338</v>
+        <v>14.88942468998061</v>
       </c>
     </row>
     <row r="10">
@@ -3438,10 +3434,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>70761</v>
+        <v>8281</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3456,7 +3452,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Lvl</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3471,12 +3467,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Mod</t>
+          <t>Gtl</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ClearCr</t>
+          <t>Sawyer</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -3500,16 +3496,16 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>1975</v>
+        <v>1965</v>
       </c>
       <c r="T10" t="n">
-        <v>1975</v>
+        <v>1965</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3518,17 +3514,17 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>WdShngl</t>
+          <t>CompShg</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Plywood</t>
+          <t>MetalSd</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Plywood</t>
+          <t>MetalSd</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3556,51 +3552,51 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Rec</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>553</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>BLQ</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>311</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>864</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>GasA</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>Gd</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Gd</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>ALQ</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>655</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Unf</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>878</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1533</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>GasA</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3612,7 +3608,7 @@
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>1533</v>
+        <v>864</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3621,29 +3617,29 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>1533</v>
+        <v>864</v>
       </c>
       <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2</v>
-      </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ10" t="n">
         <v>1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="BB10" t="n">
@@ -3655,20 +3651,20 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Po</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>Attchd</t>
+          <t>Detchd</t>
         </is>
       </c>
       <c r="BG10" t="n">
-        <v>1975</v>
+        <v>1965</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
@@ -3676,10 +3672,10 @@
         </is>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>576</v>
+        <v>360</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -3697,13 +3693,13 @@
         </is>
       </c>
       <c r="BN10" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -3715,7 +3711,11 @@
         <v>0</v>
       </c>
       <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>GdWo</t>
+        </is>
+      </c>
       <c r="BV10" t="inlineStr"/>
       <c r="BW10" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
         <v>12</v>
       </c>
       <c r="BY10" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
@@ -3737,19 +3737,19 @@
         </is>
       </c>
       <c r="CB10" t="n">
-        <v>280000</v>
+        <v>62383</v>
       </c>
       <c r="CC10" t="n">
-        <v>222581.45</v>
+        <v>121611.6224540712</v>
       </c>
       <c r="CD10" t="n">
-        <v>57418.54999999999</v>
+        <v>-59228.62245407123</v>
       </c>
       <c r="CE10" t="n">
-        <v>57418.54999999999</v>
+        <v>59228.62245407123</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.506625</v>
+        <v>94.94353021507659</v>
       </c>
     </row>
     <row r="11">
@@ -4068,16 +4068,16 @@
         <v>40000</v>
       </c>
       <c r="CC11" t="n">
-        <v>96538.5</v>
+        <v>96367.55779157029</v>
       </c>
       <c r="CD11" t="n">
-        <v>-56538.5</v>
+        <v>-56367.55779157029</v>
       </c>
       <c r="CE11" t="n">
-        <v>56538.5</v>
+        <v>56367.55779157029</v>
       </c>
       <c r="CF11" t="n">
-        <v>141.34625</v>
+        <v>140.9188944789257</v>
       </c>
     </row>
     <row r="12">
@@ -4089,11 +4089,9 @@
           <t>RL</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>79</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>9416</v>
+        <v>15498</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4103,7 +4101,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Reg</t>
+          <t>IR1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4118,7 +4116,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Inside</t>
+          <t>Corner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4128,7 +4126,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Somerst</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4152,16 +4150,16 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="T12" t="n">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -4170,30 +4168,30 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>CompShg</t>
+          <t>WdShake</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>CemntBd</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CmentBd</t>
+          <t>HdBoard</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -4203,12 +4201,12 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>PConc</t>
+          <t>CBlock</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -4218,30 +4216,30 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Av</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>GLQ</t>
+          <t>ALQ</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1126</v>
+        <v>1165</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Unf</t>
+          <t>LwQ</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AK12" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1726</v>
+        <v>1565</v>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
@@ -4250,7 +4248,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4264,7 +4262,7 @@
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>1726</v>
+        <v>2898</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4273,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1726</v>
+        <v>2898</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -4288,18 +4286,18 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ12" t="n">
         <v>1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
@@ -4320,7 +4318,7 @@
         </is>
       </c>
       <c r="BG12" t="n">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
@@ -4328,10 +4326,10 @@
         </is>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>786</v>
+        <v>665</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -4349,19 +4347,19 @@
         </is>
       </c>
       <c r="BN12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
@@ -4373,49 +4371,51 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BY12" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Abnorml</t>
         </is>
       </c>
       <c r="CB12" t="n">
-        <v>311872</v>
+        <v>287000</v>
       </c>
       <c r="CC12" t="n">
-        <v>261282.2</v>
+        <v>340917.5935352216</v>
       </c>
       <c r="CD12" t="n">
-        <v>50589.79999999999</v>
+        <v>-53917.59353522165</v>
       </c>
       <c r="CE12" t="n">
-        <v>50589.79999999999</v>
+        <v>53917.59353522165</v>
       </c>
       <c r="CF12" t="n">
-        <v>16.22133439359737</v>
+        <v>18.78661795652322</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>79</v>
+      </c>
       <c r="D13" t="n">
-        <v>11029</v>
+        <v>9416</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IR1</t>
+          <t>Reg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Corner</t>
+          <t>Inside</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NWAmes</t>
+          <t>Somerst</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PosA</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -4470,24 +4470,24 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2Story</t>
+          <t>1Story</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>1968</v>
+        <v>2007</v>
       </c>
       <c r="T13" t="n">
-        <v>1984</v>
+        <v>2007</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Gable</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -4497,25 +4497,25 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>HdBoard</t>
+          <t>CemntBd</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>HdBoard</t>
+          <t>CmentBd</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>BrkFace</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>CBlock</t>
+          <t>PConc</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -4540,16 +4540,16 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>BLQ</t>
+          <t>GLQ</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>619</v>
+        <v>1126</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>435</v>
+        <v>600</v>
       </c>
       <c r="AL13" t="n">
-        <v>1054</v>
+        <v>1726</v>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4586,16 +4586,16 @@
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>1512</v>
+        <v>1726</v>
       </c>
       <c r="AR13" t="n">
-        <v>1142</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2654</v>
+        <v>1726</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
@@ -4607,21 +4607,21 @@
         <v>2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ13" t="n">
         <v>1</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="BB13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
@@ -4642,18 +4642,18 @@
         </is>
       </c>
       <c r="BG13" t="n">
-        <v>1968</v>
+        <v>2007</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>Unf</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>619</v>
+        <v>786</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="BO13" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="BP13" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -4695,51 +4695,49 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BY13" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>New</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="CB13" t="n">
-        <v>250000</v>
+        <v>311872</v>
       </c>
       <c r="CC13" t="n">
-        <v>201625.59</v>
+        <v>261740.6531236213</v>
       </c>
       <c r="CD13" t="n">
-        <v>48374.41</v>
+        <v>50131.34687637867</v>
       </c>
       <c r="CE13" t="n">
-        <v>48374.41</v>
+        <v>50131.34687637867</v>
       </c>
       <c r="CF13" t="n">
-        <v>19.349764</v>
+        <v>16.07433398201142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>85</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>11049</v>
+        <v>12800</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4754,7 +4752,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lvl</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4764,17 +4762,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Corner</t>
+          <t>Inside</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Gtl</t>
+          <t>Mod</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CollgCr</t>
+          <t>SawyerW</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -4794,20 +4792,20 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1Story</t>
+          <t>SLvl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
         <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="T14" t="n">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -4821,21 +4819,21 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>VinylSd</t>
+          <t>Wd Sdng</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>VinylSd</t>
+          <t>Wd Sdng</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>BrkFace</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -4854,7 +4852,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -4864,30 +4862,30 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Av</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>GLQ</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>1518</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>Unf</t>
         </is>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Unf</t>
-        </is>
-      </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1234</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1234</v>
+        <v>1518</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -4896,7 +4894,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4910,7 +4908,7 @@
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>1234</v>
+        <v>1644</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4919,13 +4917,13 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1234</v>
+        <v>1644</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
         <v>2</v>
@@ -4934,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ14" t="n">
         <v>1</v>
@@ -4945,7 +4943,7 @@
         </is>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
@@ -4953,27 +4951,31 @@
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
       <c r="BF14" t="inlineStr">
         <is>
           <t>Attchd</t>
         </is>
       </c>
       <c r="BG14" t="n">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>RFn</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>484</v>
+        <v>569</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -4991,10 +4993,10 @@
         </is>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BO14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
         <v>0</v>
@@ -5003,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
@@ -5015,10 +5017,10 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BY14" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
@@ -5031,33 +5033,35 @@
         </is>
       </c>
       <c r="CB14" t="n">
-        <v>179900</v>
+        <v>275000</v>
       </c>
       <c r="CC14" t="n">
-        <v>228029.91</v>
+        <v>227589.9559035241</v>
       </c>
       <c r="CD14" t="n">
-        <v>-48129.91</v>
+        <v>47410.0440964759</v>
       </c>
       <c r="CE14" t="n">
-        <v>48129.91</v>
+        <v>47410.0440964759</v>
       </c>
       <c r="CF14" t="n">
-        <v>26.75370205669817</v>
+        <v>17.24001603508215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RL</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>C (all)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
       <c r="D15" t="n">
-        <v>12800</v>
+        <v>9000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5072,7 +5076,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Lvl</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5087,12 +5091,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Mod</t>
+          <t>Gtl</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SawyerW</t>
+          <t>IDOTRR</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5112,20 +5116,20 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>SLvl</t>
+          <t>1Story</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>1989</v>
+        <v>1949</v>
       </c>
       <c r="T15" t="n">
-        <v>1989</v>
+        <v>1950</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -5139,25 +5143,25 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Wd Sdng</t>
+          <t>AsbShng</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Wd Sdng</t>
+          <t>AsbShng</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>BrkFace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -5167,12 +5171,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>PConc</t>
+          <t>CBlock</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -5182,16 +5186,16 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Av</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>GLQ</t>
+          <t>BLQ</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>1518</v>
+        <v>50</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -5202,10 +5206,10 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AL15" t="n">
-        <v>1518</v>
+        <v>480</v>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
@@ -5214,21 +5218,21 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>SBrkr</t>
+          <t>FuseA</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>1644</v>
+        <v>480</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -5237,33 +5241,33 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>1644</v>
+        <v>480</v>
       </c>
       <c r="AU15" t="n">
         <v>1</v>
       </c>
       <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>2</v>
       </c>
       <c r="AZ15" t="n">
         <v>1</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
@@ -5271,31 +5275,27 @@
         </is>
       </c>
       <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Detchd</t>
+        </is>
+      </c>
+      <c r="BG15" t="n">
+        <v>1958</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Unf</t>
+        </is>
+      </c>
+      <c r="BI15" t="n">
         <v>1</v>
       </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>Attchd</t>
-        </is>
-      </c>
-      <c r="BG15" t="n">
-        <v>1989</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>Fin</t>
-        </is>
-      </c>
-      <c r="BI15" t="n">
-        <v>2</v>
-      </c>
       <c r="BJ15" t="n">
-        <v>569</v>
+        <v>308</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="BN15" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
@@ -5337,10 +5337,10 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BY15" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
@@ -5349,23 +5349,23 @@
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnorml</t>
         </is>
       </c>
       <c r="CB15" t="n">
-        <v>275000</v>
+        <v>35311</v>
       </c>
       <c r="CC15" t="n">
-        <v>227731.82</v>
+        <v>82148.7906139714</v>
       </c>
       <c r="CD15" t="n">
-        <v>47268.17999999999</v>
+        <v>-46837.7906139714</v>
       </c>
       <c r="CE15" t="n">
-        <v>47268.17999999999</v>
+        <v>46837.7906139714</v>
       </c>
       <c r="CF15" t="n">
-        <v>17.18842909090909</v>
+        <v>132.643625538703</v>
       </c>
     </row>
     <row r="16">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C (all)</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>9000</v>
+        <v>9591</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IDOTRR</t>
+          <t>NridgHt</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5440,20 +5440,20 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
-        <v>1949</v>
+        <v>2004</v>
       </c>
       <c r="T16" t="n">
-        <v>1950</v>
+        <v>2005</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Gable</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -5463,25 +5463,25 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>AsbShng</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>AsbShng</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>BrkFace</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>CBlock</t>
+          <t>PConc</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -5511,11 +5511,11 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>BLQ</t>
+          <t>GLQ</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>50</v>
+        <v>1088</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -5526,10 +5526,10 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>430</v>
+        <v>625</v>
       </c>
       <c r="AL16" t="n">
-        <v>480</v>
+        <v>1713</v>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
@@ -5538,21 +5538,21 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>FuseA</t>
+          <t>SBrkr</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>480</v>
+        <v>1713</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>480</v>
+        <v>1713</v>
       </c>
       <c r="AU16" t="n">
         <v>1</v>
@@ -5570,24 +5570,24 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
         <v>1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="BB16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
@@ -5595,27 +5595,31 @@
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Gd</t>
+        </is>
+      </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>Detchd</t>
+          <t>Attchd</t>
         </is>
       </c>
       <c r="BG16" t="n">
-        <v>1958</v>
+        <v>2004</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Unf</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="BI16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>308</v>
+        <v>856</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -5636,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BP16" t="n">
         <v>0</v>
@@ -5645,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
@@ -5657,10 +5661,10 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BY16" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
@@ -5669,23 +5673,23 @@
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>Abnorml</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="CB16" t="n">
-        <v>35311</v>
+        <v>274900</v>
       </c>
       <c r="CC16" t="n">
-        <v>82543.5</v>
+        <v>320497.6409085433</v>
       </c>
       <c r="CD16" t="n">
-        <v>-47232.5</v>
+        <v>-45597.64090854325</v>
       </c>
       <c r="CE16" t="n">
-        <v>47232.5</v>
+        <v>45597.64090854325</v>
       </c>
       <c r="CF16" t="n">
-        <v>133.7614341140155</v>
+        <v>16.58699196382075</v>
       </c>
     </row>
     <row r="17">
@@ -5697,9 +5701,11 @@
           <t>RL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>85</v>
+      </c>
       <c r="D17" t="n">
-        <v>15498</v>
+        <v>11049</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -5709,7 +5715,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IR1</t>
+          <t>Reg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5734,7 +5740,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>CollgCr</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5761,32 +5767,32 @@
         <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
-        <v>1976</v>
+        <v>2007</v>
       </c>
       <c r="T17" t="n">
-        <v>1976</v>
+        <v>2007</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Gable</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>WdShake</t>
+          <t>CompShg</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>HdBoard</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5809,12 +5815,12 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>CBlock</t>
+          <t>PConc</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -5829,25 +5835,25 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>ALQ</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>1165</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>LwQ</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1234</v>
       </c>
       <c r="AL17" t="n">
-        <v>1565</v>
+        <v>1234</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -5856,7 +5862,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5870,7 +5876,7 @@
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>2898</v>
+        <v>1234</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5879,10 +5885,10 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2898</v>
+        <v>1234</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -5894,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ17" t="n">
         <v>1</v>
@@ -5905,7 +5911,7 @@
         </is>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
@@ -5913,31 +5919,27 @@
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>Gd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="inlineStr">
         <is>
           <t>Attchd</t>
         </is>
       </c>
       <c r="BG17" t="n">
-        <v>1976</v>
+        <v>2007</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>RFn</t>
         </is>
       </c>
       <c r="BI17" t="n">
         <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>665</v>
+        <v>484</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -5958,10 +5960,10 @@
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="BP17" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
@@ -5979,35 +5981,35 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BY17" t="n">
         <v>2008</v>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>Abnorml</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="CB17" t="n">
-        <v>287000</v>
+        <v>179900</v>
       </c>
       <c r="CC17" t="n">
-        <v>334155.27</v>
+        <v>225284.718080313</v>
       </c>
       <c r="CD17" t="n">
-        <v>-47155.27000000002</v>
+        <v>-45384.71808031297</v>
       </c>
       <c r="CE17" t="n">
-        <v>47155.27000000002</v>
+        <v>45384.71808031297</v>
       </c>
       <c r="CF17" t="n">
-        <v>16.43040766550524</v>
+        <v>25.22774768221955</v>
       </c>
     </row>
     <row r="18">
@@ -6322,32 +6324,30 @@
         <v>285000</v>
       </c>
       <c r="CC18" t="n">
-        <v>329557.56</v>
+        <v>328051.7878686152</v>
       </c>
       <c r="CD18" t="n">
-        <v>-44557.56</v>
+        <v>-43051.78786861524</v>
       </c>
       <c r="CE18" t="n">
-        <v>44557.56</v>
+        <v>43051.78786861524</v>
       </c>
       <c r="CF18" t="n">
-        <v>15.63423157894737</v>
+        <v>15.10589048021587</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>91</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>11643</v>
+        <v>11029</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Reg</t>
+          <t>IR1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Inside</t>
+          <t>Corner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NAmes</t>
+          <t>NWAmes</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Artery</t>
+          <t>PosA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Duplex</t>
+          <t>1Fam</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -6406,16 +6406,16 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S19" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="T19" t="n">
-        <v>1969</v>
+        <v>1984</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>MetalSd</t>
+          <t>HdBoard</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MetalSd</t>
+          <t>HdBoard</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>368</v>
+        <v>220</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -6472,16 +6472,16 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>LwQ</t>
+          <t>BLQ</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>500</v>
+        <v>619</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>748</v>
+        <v>435</v>
       </c>
       <c r="AL19" t="n">
-        <v>1248</v>
+        <v>1054</v>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
@@ -6518,70 +6518,74 @@
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>1338</v>
+        <v>1512</v>
       </c>
       <c r="AR19" t="n">
-        <v>1296</v>
+        <v>1142</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2634</v>
+        <v>2654</v>
       </c>
       <c r="AU19" t="n">
         <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
         <v>2</v>
       </c>
       <c r="AX19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Gd</t>
+        </is>
+      </c>
+      <c r="BB19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>Gd</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>Attchd</t>
+        </is>
+      </c>
+      <c r="BG19" t="n">
+        <v>1968</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>Unf</t>
+        </is>
+      </c>
+      <c r="BI19" t="n">
         <v>2</v>
       </c>
-      <c r="AY19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="BB19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>Typ</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>Detchd</t>
-        </is>
-      </c>
-      <c r="BG19" t="n">
-        <v>1969</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>Unf</t>
-        </is>
-      </c>
-      <c r="BI19" t="n">
-        <v>4</v>
-      </c>
       <c r="BJ19" t="n">
-        <v>968</v>
+        <v>619</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
         <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BP19" t="n">
         <v>0</v>
@@ -6611,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="BS19" t="n">
         <v>0</v>
@@ -6626,7 +6630,7 @@
         <v>8</v>
       </c>
       <c r="BY19" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
@@ -6639,24 +6643,24 @@
         </is>
       </c>
       <c r="CB19" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="CC19" t="n">
-        <v>155836.91</v>
+        <v>208390.7305205344</v>
       </c>
       <c r="CD19" t="n">
-        <v>44163.09</v>
+        <v>41609.26947946558</v>
       </c>
       <c r="CE19" t="n">
-        <v>44163.09</v>
+        <v>41609.26947946558</v>
       </c>
       <c r="CF19" t="n">
-        <v>22.081545</v>
+        <v>16.64370779178623</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -6664,10 +6668,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D20" t="n">
-        <v>12615</v>
+        <v>13682</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -6677,12 +6681,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Reg</t>
+          <t>IR2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lvl</t>
+          <t>HLS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6692,7 +6696,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Corner</t>
+          <t>CulDSac</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -6702,7 +6706,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Edwards</t>
+          <t>StoneBr</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -6722,24 +6726,24 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1Story</t>
+          <t>2Story</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>1950</v>
+        <v>2006</v>
       </c>
       <c r="T20" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Gable</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -6749,25 +6753,25 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>WdShing</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Wd Shng</t>
+          <t>VinylSd</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>BrkFace</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -6777,31 +6781,31 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>CBlock</t>
+          <t>PConc</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>Gd</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Av</t>
-        </is>
-      </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>ALQ</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -6812,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>725</v>
+        <v>1410</v>
       </c>
       <c r="AL20" t="n">
-        <v>1202</v>
+        <v>1410</v>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
@@ -6824,7 +6828,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Ex</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -6838,31 +6842,31 @@
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>2158</v>
+        <v>1426</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2158</v>
+        <v>2945</v>
       </c>
       <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX20" t="n">
         <v>1</v>
       </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
       <c r="AY20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ20" t="n">
         <v>1</v>
@@ -6873,7 +6877,7 @@
         </is>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
@@ -6890,22 +6894,22 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>Attchd</t>
+          <t>BuiltIn</t>
         </is>
       </c>
       <c r="BG20" t="n">
-        <v>1950</v>
+        <v>2006</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>Unf</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="BI20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>576</v>
+        <v>641</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -6923,13 +6927,13 @@
         </is>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="BO20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BQ20" t="n">
         <v>0</v>
@@ -6941,61 +6945,57 @@
         <v>0</v>
       </c>
       <c r="BT20" t="inlineStr"/>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>MnPrv</t>
-        </is>
-      </c>
+      <c r="BU20" t="inlineStr"/>
       <c r="BV20" t="inlineStr"/>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BY20" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>New</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="CB20" t="n">
-        <v>243000</v>
+        <v>438780</v>
       </c>
       <c r="CC20" t="n">
-        <v>199101.41</v>
+        <v>397782.9401881314</v>
       </c>
       <c r="CD20" t="n">
-        <v>43898.59</v>
+        <v>40997.05981186865</v>
       </c>
       <c r="CE20" t="n">
-        <v>43898.59</v>
+        <v>40997.05981186865</v>
       </c>
       <c r="CF20" t="n">
-        <v>18.0652633744856</v>
+        <v>9.343420350031598</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>C (all)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n">
-        <v>8769</v>
+        <v>7500</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Corner</t>
+          <t>Inside</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NridgHt</t>
+          <t>IDOTRR</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -7045,29 +7045,29 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>TwnhsE</t>
+          <t>1Fam</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1Story</t>
+          <t>1.5Fin</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>2008</v>
+        <v>1920</v>
       </c>
       <c r="T21" t="n">
-        <v>2008</v>
+        <v>1950</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Gable</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -7087,30 +7087,30 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>BrkFace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>PConc</t>
+          <t>CBlock</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -7125,11 +7125,11 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>GLQ</t>
+          <t>Unf</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>1540</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>162</v>
+        <v>698</v>
       </c>
       <c r="AL21" t="n">
-        <v>1702</v>
+        <v>698</v>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -7162,23 +7162,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>SBrkr</t>
+          <t>FuseA</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>1702</v>
+        <v>698</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>1702</v>
+        <v>1128</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -7187,21 +7187,21 @@
         <v>1</v>
       </c>
       <c r="AX21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ21" t="n">
         <v>1</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="BB21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
@@ -7209,31 +7209,27 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>Gd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>Attchd</t>
+          <t>Detchd</t>
         </is>
       </c>
       <c r="BG21" t="n">
-        <v>2008</v>
+        <v>1980</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>RFn</t>
         </is>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1052</v>
+        <v>528</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -7251,19 +7247,19 @@
         </is>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BO21" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="BQ21" t="n">
         <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
         <v>0</v>
@@ -7275,35 +7271,35 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BY21" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Abnorml</t>
         </is>
       </c>
       <c r="CB21" t="n">
-        <v>367294</v>
+        <v>68400</v>
       </c>
       <c r="CC21" t="n">
-        <v>411164.66</v>
+        <v>108032.7799065057</v>
       </c>
       <c r="CD21" t="n">
-        <v>-43870.65999999997</v>
+        <v>-39632.77990650573</v>
       </c>
       <c r="CE21" t="n">
-        <v>43870.65999999997</v>
+        <v>39632.77990650573</v>
       </c>
       <c r="CF21" t="n">
-        <v>11.94428986043877</v>
+        <v>57.94266068202592</v>
       </c>
     </row>
   </sheetData>
